--- a/data/trans_orig/IP16A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Clase-trans_orig.xlsx
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32969</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>51847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69513</t>
+          <t>68896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>32208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>37753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54001</t>
+          <t>54802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31745</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81989</t>
+          <t>83013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82222</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100920</t>
+          <t>102163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171522</t>
+          <t>171169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198509</t>
+          <t>198378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65064</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>87643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114499</t>
+          <t>114852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44416</t>
+          <t>44540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26662</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65034</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>82714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>72480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125393</t>
+          <t>125872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150338</t>
+          <t>151231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>40106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57786</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62292</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89517</t>
+          <t>88624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114462</t>
+          <t>113983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22918</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16361</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36625</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66925</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64704</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>110068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>46773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67521</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18751</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85182</t>
+          <t>85293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132868</t>
+          <t>131596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>92736</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116618</t>
+          <t>117560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186584</t>
+          <t>186492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241452</t>
+          <t>245396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62691</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87701</t>
+          <t>86573</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113245</t>
+          <t>109301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>168113</t>
+          <t>168205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,47 +1066,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,47 +1409,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,47 +1752,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,47 +2095,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2438,47 +2438,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2781,47 +2781,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3358,72 +3358,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11056</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18412</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13586</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9544</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9803</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15125</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11084</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18569</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -3471,72 +3471,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6853</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3566</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10922</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7334</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4240</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11376</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3920</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11117</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6853</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10894</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -3584,57 +3584,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3701,72 +3701,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9994</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>17237</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13077</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20166</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13340</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20091</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>75,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7340</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4434</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9912</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>60,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>28401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3814,72 +3814,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7772</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>5666</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9826</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7654</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -3927,57 +3927,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4049,67 +4049,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>9623</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11740</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>9416</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6532</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10853</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10843</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9623</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11735</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -4157,72 +4157,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4939</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5800</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -4270,57 +4270,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11471</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11471</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11471</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4387,72 +4387,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26925</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39694</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27370</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21583</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32593</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21546</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32395</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>57,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33220</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26702</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39228</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>51981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68896</t>
+          <t>68659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -4500,72 +4500,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25690</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19216</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31985</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20369</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15146</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26156</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15344</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26193</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>42,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25690</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19682</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32208</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37753</t>
+          <t>37990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54802</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>47739</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>47739</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>47739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19059</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13725</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22320</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19320</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23297</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14640</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22764</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19059</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14695</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22865</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -4848,67 +4848,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>8978</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14312</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>9325</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13820</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5881</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8978</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5172</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13342</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28037</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28037</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28037</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>28037</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>28037</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>28037</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11027</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>35,73%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4948</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6402</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6403</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>70,13%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10845</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -5186,72 +5186,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>64,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2108</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4868</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4944</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>29,87%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>68,99%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5648</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>92515</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>82488</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>101950</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>56,01%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,22%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>91878</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>83013</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>101061</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>83313</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100465</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>66,23%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>92515</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>83132</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>102163</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171169</t>
+          <t>170904</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198378</t>
+          <t>196952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -5529,72 +5529,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>54771</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>45336</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>64798</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,99%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>46857</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>37674</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>55722</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>38270</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>55422</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>33,77%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>54771</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>45123</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>64154</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87643</t>
+          <t>89069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114852</t>
+          <t>115117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138735</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138735</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138735</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +5825,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5993,72 +5993,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7288</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10530</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4169</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9360</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5942</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -6111,67 +6111,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>8384</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4963</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>8555</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5313</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11817</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11674</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8384</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11802</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -6219,57 +6219,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6336,72 +6336,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12443</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8965</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15731</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7708</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4760</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10113</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4928</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10167</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12443</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8485</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15437</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>65,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -6449,72 +6449,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10097</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4288</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7236</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7068</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3625</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10577</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -6562,57 +6562,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6679,72 +6679,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6460</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3951</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8125</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8236</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2879</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -6792,72 +6792,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4763</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2386</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4895</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5047</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4763</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7388</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -6905,57 +6905,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7022,72 +7022,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15587</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11029</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20375</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28129</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22404</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33534</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22704</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33208</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15587</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10674</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20434</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>51544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -7135,72 +7135,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18937</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14149</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23495</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18360</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12955</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24085</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13281</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23785</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>39,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18937</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14090</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>23850</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44540</t>
+          <t>43668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -7248,57 +7248,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7365,72 +7365,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12692</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20560</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15490</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11169</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19438</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11208</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20007</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17061</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20511</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -7478,72 +7478,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12970</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>11131</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7183</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15452</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15413</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8601</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13062</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -7591,57 +7591,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7708,72 +7708,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>39,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>67,8%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>9060</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5920</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11312</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>69,56%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>45,45%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3907</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6724</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>39,96%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -7821,72 +7821,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8226</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>60,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>84,12%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7105</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7189</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>30,44%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3054</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7910</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>60,04%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -7934,57 +7934,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8051,72 +8051,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>63861</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>54141</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>72017</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,26%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>61,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>74135</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>65472</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>82714</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>65030</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>82282</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>60,36%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>63861</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>54675</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>72480</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,57%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125872</t>
+          <t>125862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151231</t>
+          <t>150224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -8164,72 +8164,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>53174</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>45018</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>62894</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,43%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>38,47%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,74%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>48685</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>40106</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>57348</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>40538</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>57790</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,64%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,65%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>53174</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>44555</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>62360</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>45,43%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>88624</t>
+          <t>89631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113983</t>
+          <t>113993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -8277,57 +8277,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8628,72 +8628,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15993</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10057</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20156</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12421</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8489</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16597</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>28541</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -8741,72 +8741,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12847</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8684</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18783</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12431</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8255</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16363</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -8854,57 +8854,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>24153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -9084,72 +9084,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11127</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8381</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -9197,57 +9197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9314,72 +9314,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11002</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -9427,72 +9427,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7154</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4452</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6748</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -9540,57 +9540,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9657,72 +9657,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30802</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22006</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48928</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29608</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>67793</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83468</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>45033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110068</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -9770,72 +9770,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13569</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27738</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>27453</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8588</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46773</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21303</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>30149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -9883,57 +9883,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10000,72 +10000,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14033</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23260</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16004</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11047</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36538</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -10113,72 +10113,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8910</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18137</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12902</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8733</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17859</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>44,64%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -10226,57 +10226,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10343,72 +10343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10299</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>48,32%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8262</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -10456,72 +10456,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7294</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10540</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>51,68%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>74,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6800</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3959</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9557</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>55,65%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,2%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10686,72 +10686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>96255</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>83852</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>107725</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>59,23%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>102968</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>85293</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>131596</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>58,71%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>75,03%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>105326</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92736</t>
+          <t>66612</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117560</t>
+          <t>85932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>208295</t>
+          <t>173222</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>158378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245396</t>
+          <t>187591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -10799,72 +10799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>66265</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>54795</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>78668</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>72419</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>43791</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>90094</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>73983</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61749</t>
+          <t>54804</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>74124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>146402</t>
+          <t>130035</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>109301</t>
+          <t>115666</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>168205</t>
+          <t>144879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -10912,57 +10912,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
